--- a/request_forms/029_social_media_insights_request_form--request_forms.xlsx
+++ b/request_forms/029_social_media_insights_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1338,34 +1338,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>social_media_platform_choices</t>
+          <t>analytics_tool_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>social_media_platform_choices</t>
+          <t>analytics_tool_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>hootsuite</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Hootsuite</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>sprout</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Sprout</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hootsuite</t>
+          <t>brand24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hootsuite</t>
+          <t>Brand24</t>
         </is>
       </c>
     </row>
@@ -1428,46 +1428,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sprout</t>
+          <t>agorapulse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sprout</t>
+          <t>Agorapulse</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>analytics_tool_choices</t>
+          <t>description_of_insights_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>brand24</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brand24</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>analytics_tool_choices</t>
+          <t>description_of_insights_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>agorapulse</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Agorapulse</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1496,46 +1496,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>description_of_insights_choices</t>
+          <t>time_period_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>30_days</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>30 Days</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>description_of_insights_choices</t>
+          <t>time_period_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>60_days</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>60 Days</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30_days</t>
+          <t>90_days</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>30 Days</t>
+          <t>90 Days</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>60_days</t>
+          <t>180_days</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>60 Days</t>
+          <t>180 Days</t>
         </is>
       </c>
     </row>
@@ -1581,46 +1581,46 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90_days</t>
+          <t>365_days</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>90 Days</t>
+          <t>365 Days</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>time_period_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>180_days</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>180 Days</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>time_period_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>365_days</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>365 Days</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1632,46 +1632,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>data_points_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>frequency_choices</t>
+          <t>data_points_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1700,46 +1700,46 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>data_points_choices</t>
+          <t>data_types_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>engagement</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>data_points_choices</t>
+          <t>data_types_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>sentiment</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Sentiment</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>engagement</t>
+          <t>keyword</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Engagement</t>
+          <t>Keyword</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sentiment</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sentiment</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1785,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>keyword</t>
+          <t>reach</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Reach</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>impressions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Impressions</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>reach</t>
+          <t>views</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Reach</t>
+          <t>Views</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>impressions</t>
+          <t>clicks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Impressions</t>
+          <t>Clicks</t>
         </is>
       </c>
     </row>
@@ -1853,46 +1853,46 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>views</t>
+          <t>click-through-rate</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Views</t>
+          <t>Click-Through-Rate</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>data_types_choices</t>
+          <t>request_reason_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>clicks</t>
+          <t>internal</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Clicks</t>
+          <t>Internal</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>data_types_choices</t>
+          <t>request_reason_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>click-through-rate</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Click-Through-Rate</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>internal</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>competitor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Competitor</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>compliance</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Compliance</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>competitor</t>
+          <t>legal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Competitor</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
@@ -1972,44 +1972,10 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>compliance</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>request_reason_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>legal</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>request_reason_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
